--- a/data/ccp_news_all.xlsx
+++ b/data/ccp_news_all.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1464"/>
+  <dimension ref="A1:F1470"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.58203125" defaultRowHeight="17.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="2" min="1" max="1"/>
@@ -38811,108 +38811,270 @@
       </c>
     </row>
     <row r="1461">
-      <c r="A1461" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1461" t="inlineStr">
+      <c r="A1461" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1461" s="0" t="inlineStr">
         <is>
           <t>Cboe Clear U.S. Approved to Expand Clearing Capabilities</t>
         </is>
       </c>
-      <c r="C1461" t="inlineStr">
+      <c r="C1461" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/cboe-clear-u-s-approved-to-expand-clearing-capabilities/</t>
         </is>
       </c>
-      <c r="D1461" t="inlineStr">
+      <c r="D1461" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1461" t="inlineStr">
+      <c r="E1461" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1462">
-      <c r="A1462" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1462" t="inlineStr">
+      <c r="A1462" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1462" s="0" t="inlineStr">
         <is>
           <t>Kalshi Launches Sector KPI Contracts With Carbon Arc</t>
         </is>
       </c>
-      <c r="C1462" t="inlineStr">
+      <c r="C1462" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/kalshi-launches-sector-kpi-contracts-with-carbon-arc/</t>
         </is>
       </c>
-      <c r="D1462" t="inlineStr">
+      <c r="D1462" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1462" t="inlineStr">
+      <c r="E1462" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1463">
-      <c r="A1463" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1463" t="inlineStr">
+      <c r="A1463" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1463" s="0" t="inlineStr">
         <is>
           <t>MarketAxess Q3 Average Daily Volume Increases 13%</t>
         </is>
       </c>
-      <c r="C1463" t="inlineStr">
+      <c r="C1463" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/marketaxess-q3-average-daily-volume-increases-13/</t>
         </is>
       </c>
-      <c r="D1463" t="inlineStr">
+      <c r="D1463" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1463" t="inlineStr">
+      <c r="E1463" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1464">
-      <c r="A1464" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1464" t="inlineStr">
+      <c r="A1464" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1464" s="0" t="inlineStr">
         <is>
           <t>Sustainable Finance Regains Momentum</t>
         </is>
       </c>
-      <c r="C1464" t="inlineStr">
+      <c r="C1464" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/sustainable-finance-regains-momentum/</t>
         </is>
       </c>
-      <c r="D1464" t="inlineStr">
+      <c r="D1464" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1464" t="inlineStr">
+      <c r="E1464" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>The Common Domain Model: A User Journey from Concept to Production</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/26/the-common-domain-model-a-user-journey-from-concept-to-production/</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>CIB in ‘Golden Window for Growth’</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/corporate-and-investment-banking-in-golden-window-for-growth/</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>The Power of Visibility: Moving the Needle for Women in Finance</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/the-power-of-visibility-moving-the-needle-for-women-in-finance/</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>Risk.net</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Equity derivatives house of the year: UBS</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>https://www.risk.net/awards/7964321/equity-derivatives-house-of-the-year-ubs</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>CIBC: investors should hedge on UST repo clearing impact</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>https://finadium.com/cibc-investors-should-hedge-on-ust-repo-clearing-impact/</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>HKMA names primary market makers for RMB22bn repo facility</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>https://finadium.com/hkma-names-primary-market-makers-for-rmb22bn-repo-facility/</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/ccp_news_all.xlsx
+++ b/data/ccp_news_all.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1470"/>
+  <dimension ref="A1:F1479"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.58203125" defaultRowHeight="17.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="2" min="1" max="1"/>
@@ -38919,162 +38919,405 @@
       </c>
     </row>
     <row r="1465">
-      <c r="A1465" t="inlineStr">
+      <c r="A1465" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1465" t="inlineStr">
+      <c r="B1465" s="0" t="inlineStr">
         <is>
           <t>The Common Domain Model: A User Journey from Concept to Production</t>
         </is>
       </c>
-      <c r="C1465" t="inlineStr">
+      <c r="C1465" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/26/the-common-domain-model-a-user-journey-from-concept-to-production/</t>
         </is>
       </c>
-      <c r="D1465" t="inlineStr">
+      <c r="D1465" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1465" t="inlineStr">
+      <c r="E1465" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1466">
-      <c r="A1466" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1466" t="inlineStr">
+      <c r="A1466" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1466" s="0" t="inlineStr">
         <is>
           <t>CIB in ‘Golden Window for Growth’</t>
         </is>
       </c>
-      <c r="C1466" t="inlineStr">
+      <c r="C1466" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/corporate-and-investment-banking-in-golden-window-for-growth/</t>
         </is>
       </c>
-      <c r="D1466" t="inlineStr">
+      <c r="D1466" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1466" t="inlineStr">
+      <c r="E1466" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1467">
-      <c r="A1467" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1467" t="inlineStr">
+      <c r="A1467" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1467" s="0" t="inlineStr">
         <is>
           <t>The Power of Visibility: Moving the Needle for Women in Finance</t>
         </is>
       </c>
-      <c r="C1467" t="inlineStr">
+      <c r="C1467" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/the-power-of-visibility-moving-the-needle-for-women-in-finance/</t>
         </is>
       </c>
-      <c r="D1467" t="inlineStr">
+      <c r="D1467" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1467" t="inlineStr">
+      <c r="E1467" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1468">
-      <c r="A1468" t="inlineStr">
+      <c r="A1468" s="0" t="inlineStr">
         <is>
           <t>Risk.net</t>
         </is>
       </c>
-      <c r="B1468" t="inlineStr">
+      <c r="B1468" s="0" t="inlineStr">
         <is>
           <t>Equity derivatives house of the year: UBS</t>
         </is>
       </c>
-      <c r="C1468" t="inlineStr">
+      <c r="C1468" s="0" t="inlineStr">
         <is>
           <t>https://www.risk.net/awards/7964321/equity-derivatives-house-of-the-year-ubs</t>
         </is>
       </c>
-      <c r="D1468" t="inlineStr">
+      <c r="D1468" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1468" t="inlineStr">
+      <c r="E1468" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1469">
-      <c r="A1469" t="inlineStr">
+      <c r="A1469" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1469" t="inlineStr">
+      <c r="B1469" s="0" t="inlineStr">
         <is>
           <t>CIBC: investors should hedge on UST repo clearing impact</t>
         </is>
       </c>
-      <c r="C1469" t="inlineStr">
+      <c r="C1469" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/cibc-investors-should-hedge-on-ust-repo-clearing-impact/</t>
         </is>
       </c>
-      <c r="D1469" t="inlineStr">
+      <c r="D1469" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1469" t="inlineStr">
+      <c r="E1469" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1470">
-      <c r="A1470" t="inlineStr">
+      <c r="A1470" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1470" t="inlineStr">
+      <c r="B1470" s="0" t="inlineStr">
         <is>
           <t>HKMA names primary market makers for RMB22bn repo facility</t>
         </is>
       </c>
-      <c r="C1470" t="inlineStr">
+      <c r="C1470" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/hkma-names-primary-market-makers-for-rmb22bn-repo-facility/</t>
         </is>
       </c>
-      <c r="D1470" t="inlineStr">
+      <c r="D1470" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="E1470" t="inlineStr">
+      <c r="E1470" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>CFTC</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>CFTC Announces Semiweekly Publication of the COT Report</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>https://www.cftc.gov/PressRoom/PressReleases/9316-26</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Accounting for Tokenized Assets as Collateral</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/27/accounting-for-tokenized-assets-as-collateral/</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>ISDA-Actrix US Treasury Repo Market Clearing Indicators September 2026</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/27/isda-actrix-us-treasury-repo-market-clearing-indicators-september-2026/</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Anthropic Pre-IPO Perpetuals Go Live</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/anthropic-pre-ipo-perpetuals-go-live/</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>First European Supranational Issues DLT Bond on Pontes</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/first-european-supranational-issues-dlt-based-bond-on-pontes/</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Global ETFs Have Records Year-to-Date Net Inflows</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/global-etfs-have-records-year-to-date-net-inflows/</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>Risk.net</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>US corporate securities settlement failures hit four-year high</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>https://www.risk.net/risk-quantum/7964279/us-corporate-securities-settlement-failures-hit-four-year-high</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>ISDA: UST cleared repo ADV up 2% at $7.7tn in September</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>https://finadium.com/isda-ust-cleared-repo-adv-up-2-at-7-7tn-in-september/</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Rates &amp; Repo 2026: Bringing the buy side into trading and clearing</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>https://finadium.com/rates-repo-2026-bringing-the-buy-side-into-trading-and-clearing/</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/ccp_news_all.xlsx
+++ b/data/ccp_news_all.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1479"/>
+  <dimension ref="A1:F1490"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.58203125" defaultRowHeight="17.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="2" min="1" max="1"/>
@@ -39081,243 +39081,540 @@
       </c>
     </row>
     <row r="1471">
-      <c r="A1471" t="inlineStr">
+      <c r="A1471" s="0" t="inlineStr">
         <is>
           <t>CFTC</t>
         </is>
       </c>
-      <c r="B1471" t="inlineStr">
+      <c r="B1471" s="0" t="inlineStr">
         <is>
           <t>CFTC Announces Semiweekly Publication of the COT Report</t>
         </is>
       </c>
-      <c r="C1471" t="inlineStr">
+      <c r="C1471" s="0" t="inlineStr">
         <is>
           <t>https://www.cftc.gov/PressRoom/PressReleases/9316-26</t>
         </is>
       </c>
-      <c r="D1471" t="inlineStr">
+      <c r="D1471" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1471" t="inlineStr">
+      <c r="E1471" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1472">
-      <c r="A1472" t="inlineStr">
+      <c r="A1472" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1472" t="inlineStr">
+      <c r="B1472" s="0" t="inlineStr">
         <is>
           <t>Accounting for Tokenized Assets as Collateral</t>
         </is>
       </c>
-      <c r="C1472" t="inlineStr">
+      <c r="C1472" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/27/accounting-for-tokenized-assets-as-collateral/</t>
         </is>
       </c>
-      <c r="D1472" t="inlineStr">
+      <c r="D1472" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1472" t="inlineStr">
+      <c r="E1472" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1473">
-      <c r="A1473" t="inlineStr">
+      <c r="A1473" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1473" t="inlineStr">
+      <c r="B1473" s="0" t="inlineStr">
         <is>
           <t>ISDA-Actrix US Treasury Repo Market Clearing Indicators September 2026</t>
         </is>
       </c>
-      <c r="C1473" t="inlineStr">
+      <c r="C1473" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/27/isda-actrix-us-treasury-repo-market-clearing-indicators-september-2026/</t>
         </is>
       </c>
-      <c r="D1473" t="inlineStr">
+      <c r="D1473" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1473" t="inlineStr">
+      <c r="E1473" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1474">
-      <c r="A1474" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1474" t="inlineStr">
+      <c r="A1474" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1474" s="0" t="inlineStr">
         <is>
           <t>Anthropic Pre-IPO Perpetuals Go Live</t>
         </is>
       </c>
-      <c r="C1474" t="inlineStr">
+      <c r="C1474" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/anthropic-pre-ipo-perpetuals-go-live/</t>
         </is>
       </c>
-      <c r="D1474" t="inlineStr">
+      <c r="D1474" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1474" t="inlineStr">
+      <c r="E1474" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1475">
-      <c r="A1475" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1475" t="inlineStr">
+      <c r="A1475" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1475" s="0" t="inlineStr">
         <is>
           <t>First European Supranational Issues DLT Bond on Pontes</t>
         </is>
       </c>
-      <c r="C1475" t="inlineStr">
+      <c r="C1475" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/first-european-supranational-issues-dlt-based-bond-on-pontes/</t>
         </is>
       </c>
-      <c r="D1475" t="inlineStr">
+      <c r="D1475" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1475" t="inlineStr">
+      <c r="E1475" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1476">
-      <c r="A1476" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1476" t="inlineStr">
+      <c r="A1476" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1476" s="0" t="inlineStr">
         <is>
           <t>Global ETFs Have Records Year-to-Date Net Inflows</t>
         </is>
       </c>
-      <c r="C1476" t="inlineStr">
+      <c r="C1476" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/global-etfs-have-records-year-to-date-net-inflows/</t>
         </is>
       </c>
-      <c r="D1476" t="inlineStr">
+      <c r="D1476" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1476" t="inlineStr">
+      <c r="E1476" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1477">
-      <c r="A1477" t="inlineStr">
+      <c r="A1477" s="0" t="inlineStr">
         <is>
           <t>Risk.net</t>
         </is>
       </c>
-      <c r="B1477" t="inlineStr">
+      <c r="B1477" s="0" t="inlineStr">
         <is>
           <t>US corporate securities settlement failures hit four-year high</t>
         </is>
       </c>
-      <c r="C1477" t="inlineStr">
+      <c r="C1477" s="0" t="inlineStr">
         <is>
           <t>https://www.risk.net/risk-quantum/7964279/us-corporate-securities-settlement-failures-hit-four-year-high</t>
         </is>
       </c>
-      <c r="D1477" t="inlineStr">
+      <c r="D1477" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1477" t="inlineStr">
+      <c r="E1477" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1478">
-      <c r="A1478" t="inlineStr">
+      <c r="A1478" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1478" t="inlineStr">
+      <c r="B1478" s="0" t="inlineStr">
         <is>
           <t>ISDA: UST cleared repo ADV up 2% at $7.7tn in September</t>
         </is>
       </c>
-      <c r="C1478" t="inlineStr">
+      <c r="C1478" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/isda-ust-cleared-repo-adv-up-2-at-7-7tn-in-september/</t>
         </is>
       </c>
-      <c r="D1478" t="inlineStr">
+      <c r="D1478" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1478" t="inlineStr">
+      <c r="E1478" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1479">
-      <c r="A1479" t="inlineStr">
+      <c r="A1479" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1479" t="inlineStr">
+      <c r="B1479" s="0" t="inlineStr">
         <is>
           <t>Rates &amp; Repo 2026: Bringing the buy side into trading and clearing</t>
         </is>
       </c>
-      <c r="C1479" t="inlineStr">
+      <c r="C1479" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/rates-repo-2026-bringing-the-buy-side-into-trading-and-clearing/</t>
         </is>
       </c>
-      <c r="D1479" t="inlineStr">
+      <c r="D1479" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1479" t="inlineStr">
+      <c r="E1479" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>ISDA/AFMA Sydney Derivatives Trading Forum: Scott O’Malia Opening Remarks</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/28/isda-afma-sydney-derivatives-trading-forum-scott-omalia-opening-remarks/</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>ISDA Publishes FpML Version 5.14</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/28/isda-publishes-fpml-version-5-14/</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Nasdaq Invests in Always-On Markets</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/nasdaq-invests-in-always-on-markets/</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>DTCC Tokenization Service Goes Live</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/dtcc-tokenization-service-goes-live/</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>CME Brazilian Real Futures Set Record After Election</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/cme-brazilian-real-futures-set-record-after-election/</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Plus500 is First FCM to Launch Kalshi Perpetuals</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/plus500-is-first-fcm-to-launch-kalshi-perpetuals/</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>Risk.net</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Basel G-Sib rule change could spare 24 banks reporting</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>https://www.risk.net/risk-quantum/7964320/basel-g-sib-rule-change-could-spare-24-banks-reporting</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>Risk.net</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Why a hybrid approach works best for AI in credit risk modelling</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>https://www.risk.net/comment/7963969/why-a-hybrid-approach-works-best-for-ai-in-credit-risk-modelling</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>DerivSource</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>DERIVSOURCE: Perpetuals, Prediction Markets Raise New Questions for Derivatives Market Structure</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>https://www.tradersmagazine.com/featured_articles/derivsource-perpetuals-and-prediction-markets-raise-new-questions-for-derivatives-market-structure/</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>DTCC tokenization services goes live with 20 participants</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>https://finadium.com/dtcc-tokenization-services-goes-live-with-20-participants/</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Video Interview: LCH RepoClear’s Michel Semaan on the growing importance of Guaranteed Sponsored Clearing</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>https://finadium.com/video-interview-lch-repoclears-michel-semaan-on-the-growing-importance-of-guaranteed-sponsored-clearing/</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/ccp_news_all.xlsx
+++ b/data/ccp_news_all.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1490"/>
+  <dimension ref="A1:F1513"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.58203125" defaultRowHeight="17.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="2" min="1" max="1"/>
@@ -39324,297 +39324,918 @@
       </c>
     </row>
     <row r="1480">
-      <c r="A1480" t="inlineStr">
+      <c r="A1480" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1480" t="inlineStr">
+      <c r="B1480" s="0" t="inlineStr">
         <is>
           <t>ISDA/AFMA Sydney Derivatives Trading Forum: Scott O’Malia Opening Remarks</t>
         </is>
       </c>
-      <c r="C1480" t="inlineStr">
+      <c r="C1480" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/28/isda-afma-sydney-derivatives-trading-forum-scott-omalia-opening-remarks/</t>
         </is>
       </c>
-      <c r="D1480" t="inlineStr">
+      <c r="D1480" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1480" t="inlineStr">
+      <c r="E1480" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1481">
-      <c r="A1481" t="inlineStr">
+      <c r="A1481" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1481" t="inlineStr">
+      <c r="B1481" s="0" t="inlineStr">
         <is>
           <t>ISDA Publishes FpML Version 5.14</t>
         </is>
       </c>
-      <c r="C1481" t="inlineStr">
+      <c r="C1481" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/28/isda-publishes-fpml-version-5-14/</t>
         </is>
       </c>
-      <c r="D1481" t="inlineStr">
+      <c r="D1481" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1481" t="inlineStr">
+      <c r="E1481" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1482">
-      <c r="A1482" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1482" t="inlineStr">
+      <c r="A1482" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1482" s="0" t="inlineStr">
         <is>
           <t>Nasdaq Invests in Always-On Markets</t>
         </is>
       </c>
-      <c r="C1482" t="inlineStr">
+      <c r="C1482" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/nasdaq-invests-in-always-on-markets/</t>
         </is>
       </c>
-      <c r="D1482" t="inlineStr">
+      <c r="D1482" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1482" t="inlineStr">
+      <c r="E1482" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1483">
-      <c r="A1483" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1483" t="inlineStr">
+      <c r="A1483" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1483" s="0" t="inlineStr">
         <is>
           <t>DTCC Tokenization Service Goes Live</t>
         </is>
       </c>
-      <c r="C1483" t="inlineStr">
+      <c r="C1483" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/dtcc-tokenization-service-goes-live/</t>
         </is>
       </c>
-      <c r="D1483" t="inlineStr">
+      <c r="D1483" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1483" t="inlineStr">
+      <c r="E1483" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1484">
-      <c r="A1484" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1484" t="inlineStr">
+      <c r="A1484" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1484" s="0" t="inlineStr">
         <is>
           <t>CME Brazilian Real Futures Set Record After Election</t>
         </is>
       </c>
-      <c r="C1484" t="inlineStr">
+      <c r="C1484" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/cme-brazilian-real-futures-set-record-after-election/</t>
         </is>
       </c>
-      <c r="D1484" t="inlineStr">
+      <c r="D1484" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1484" t="inlineStr">
+      <c r="E1484" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1485">
-      <c r="A1485" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1485" t="inlineStr">
+      <c r="A1485" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1485" s="0" t="inlineStr">
         <is>
           <t>Plus500 is First FCM to Launch Kalshi Perpetuals</t>
         </is>
       </c>
-      <c r="C1485" t="inlineStr">
+      <c r="C1485" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/plus500-is-first-fcm-to-launch-kalshi-perpetuals/</t>
         </is>
       </c>
-      <c r="D1485" t="inlineStr">
+      <c r="D1485" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1485" t="inlineStr">
+      <c r="E1485" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1486">
-      <c r="A1486" t="inlineStr">
+      <c r="A1486" s="0" t="inlineStr">
         <is>
           <t>Risk.net</t>
         </is>
       </c>
-      <c r="B1486" t="inlineStr">
+      <c r="B1486" s="0" t="inlineStr">
         <is>
           <t>Basel G-Sib rule change could spare 24 banks reporting</t>
         </is>
       </c>
-      <c r="C1486" t="inlineStr">
+      <c r="C1486" s="0" t="inlineStr">
         <is>
           <t>https://www.risk.net/risk-quantum/7964320/basel-g-sib-rule-change-could-spare-24-banks-reporting</t>
         </is>
       </c>
-      <c r="D1486" t="inlineStr">
+      <c r="D1486" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1486" t="inlineStr">
+      <c r="E1486" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1487">
-      <c r="A1487" t="inlineStr">
+      <c r="A1487" s="0" t="inlineStr">
         <is>
           <t>Risk.net</t>
         </is>
       </c>
-      <c r="B1487" t="inlineStr">
+      <c r="B1487" s="0" t="inlineStr">
         <is>
           <t>Why a hybrid approach works best for AI in credit risk modelling</t>
         </is>
       </c>
-      <c r="C1487" t="inlineStr">
+      <c r="C1487" s="0" t="inlineStr">
         <is>
           <t>https://www.risk.net/comment/7963969/why-a-hybrid-approach-works-best-for-ai-in-credit-risk-modelling</t>
         </is>
       </c>
-      <c r="D1487" t="inlineStr">
+      <c r="D1487" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1487" t="inlineStr">
+      <c r="E1487" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1488">
-      <c r="A1488" t="inlineStr">
+      <c r="A1488" s="0" t="inlineStr">
         <is>
           <t>DerivSource</t>
         </is>
       </c>
-      <c r="B1488" t="inlineStr">
+      <c r="B1488" s="0" t="inlineStr">
         <is>
           <t>DERIVSOURCE: Perpetuals, Prediction Markets Raise New Questions for Derivatives Market Structure</t>
         </is>
       </c>
-      <c r="C1488" t="inlineStr">
+      <c r="C1488" s="0" t="inlineStr">
         <is>
           <t>https://www.tradersmagazine.com/featured_articles/derivsource-perpetuals-and-prediction-markets-raise-new-questions-for-derivatives-market-structure/</t>
         </is>
       </c>
-      <c r="D1488" t="inlineStr">
+      <c r="D1488" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1488" t="inlineStr">
+      <c r="E1488" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1489">
-      <c r="A1489" t="inlineStr">
+      <c r="A1489" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1489" t="inlineStr">
+      <c r="B1489" s="0" t="inlineStr">
         <is>
           <t>DTCC tokenization services goes live with 20 participants</t>
         </is>
       </c>
-      <c r="C1489" t="inlineStr">
+      <c r="C1489" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/dtcc-tokenization-services-goes-live-with-20-participants/</t>
         </is>
       </c>
-      <c r="D1489" t="inlineStr">
+      <c r="D1489" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1489" t="inlineStr">
+      <c r="E1489" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1490">
-      <c r="A1490" t="inlineStr">
+      <c r="A1490" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1490" t="inlineStr">
+      <c r="B1490" s="0" t="inlineStr">
         <is>
           <t>Video Interview: LCH RepoClear’s Michel Semaan on the growing importance of Guaranteed Sponsored Clearing</t>
         </is>
       </c>
-      <c r="C1490" t="inlineStr">
+      <c r="C1490" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/video-interview-lch-repoclears-michel-semaan-on-the-growing-importance-of-guaranteed-sponsored-clearing/</t>
         </is>
       </c>
-      <c r="D1490" t="inlineStr">
+      <c r="D1490" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1490" t="inlineStr">
+      <c r="E1490" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>Bank of England</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Bank of England sets out approach to tokenised collateral in central clearing</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/news/2026/october/bank-of-england-sets-out-approach-to-tokenised-collateral-in-central-clearing</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>Bank of England publish</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Bank of England Weekly Report 28 October 2026</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/weekly-report/2026/28-october-2026</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>Bank of England publish</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Consultation on supervisory expectations for central counterparties seeking to accept tokenised collateral</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/paper/2026/cp/supervisory-expectations-for-ccps-seeking-to-accept-tokenised-collateral</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>ESMA</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>ESMA publishes latest edition of its newsletter</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>https://www.esma.europa.eu/press-news/esma-news/esma-publishes-latest-edition-its-newsletter-45</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>ESMA</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>ESMA proposes simpler EU Taxonomy reporting</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>https://www.esma.europa.eu/press-news/esma-news/esma-proposes-simpler-eu-taxonomy-reporting</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Moving Regulatory Reporting up a Gear with AI</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/29/moving-regulatory-reporting-up-a-gear-with-ai/</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>BIS</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>CPMI publishes analysis on how central banks support payment system safety and efficiency and trust in money in the rapidly changing payments ecosystem</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>https://www.bis.org/media-releases/20261029-cpmi-publishes-analysis-how-central-banks-support-payment-system-safety-and-efficiency-and</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>The Trade News</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>DTCC tokenisation service goes live as it ‘establishes the foundation for responsible institutional adoption at scale’</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>https://www.thetradenews.com/dtcc-tokenisation-service-goes-live-as-it-seeks-to-establish-the-foundation-for-responsible-institutional-adoption-at-scale/</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>The Trade News</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Ripple and Robinhood partner to enhance institutional access to digital assets and treasury operations</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>https://www.thetradenews.com/ripple-and-robinhood-partner-to-enhance-institutional-access-to-digital-assets-and-treasury-operations/</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>The Trade News</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>SGX and Philippine Stock Exchange join forces to boost Asian capital market ties</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>https://www.thetradenews.com/sgx-and-philippine-stock-exchange-join-forces-to-boost-asian-capital-market-ties/</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>The Trade News</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>‘Big Bang’ at 40: Are capital markets on the cusp of another revolution?</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>https://www.thetradenews.com/big-bang-at-40-are-capital-markets-on-the-cusp-of-another-revolution/</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>ICE Invests in TradeXYZ to Build Regulated Perpetual Market</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/ice-invests-in-tradexyz-to-build-regulated-perpetual-market/</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>State Street Advances Daily NAV for Private Markets</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/state-street-advances-daily-nav-for-private-markets/</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Chainlink, S&amp;P Bring Vault Assessments Onchain</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/chainlink-sp-global-ratings-bring-vault-assessments-onchain/</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>Risk.net</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Non-bank dealers urge rethink on FICC default fund reshuffle</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>https://www.risk.net/risk-management/7964301/non-bank-dealers-urge-rethink-on-ficc-default-fund-reshuffle</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Japan’s Progmat aims to tokenize bilateral JGB repo in Canton sandbox</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>https://finadium.com/japans-progmat-aims-to-tokenize-bilateral-jgb-repo-in-canton-sandbox/</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>UK DMO introduces standing repo facility and £250mn collateral pool</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>https://finadium.com/uk-dmo-introduces-standing-repo-facility-and-250mn-collateral-pool/</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Ascend and M1X Global transact first repo using USDM1 collateral</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>https://finadium.com/ascend-and-m1x-global-transact-first-repo-using-usdm1-collateral/</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>The Investor: Vietnam margin lending hits record highs</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>https://finadium.com/the-investor-vietnam-margin-lending-hits-record-highs/</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>BoE mulls how to supervise tokenized collateral for CCPs</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>https://finadium.com/boe-mulls-how-to-supervise-tokenized-collateral-for-ccps/</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>ISDA analyzes tokenized collateral under IFRS and US GAAP for SFTs</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>https://finadium.com/isda-analyzes-tokenized-collateral-under-ifrs-and-us-gaap-for-sfts/</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Tradeweb money markets ADV up 6% y/y at $1.1tn in Q3 2026</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>https://finadium.com/tradeweb-money-markets-adv-up-6-y-y-at-1-1tn-in-q3-2026/</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>ISDA to deploy four more AI agents for regulatory reporting</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>https://finadium.com/isda-to-deploy-four-more-ai-agents-for-regulatory-reporting/</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/ccp_news_all.xlsx
+++ b/data/ccp_news_all.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1513"/>
+  <dimension ref="A1:F1521"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.58203125" defaultRowHeight="17.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="2" min="1" max="1"/>
@@ -39621,621 +39621,837 @@
       </c>
     </row>
     <row r="1491">
-      <c r="A1491" t="inlineStr">
+      <c r="A1491" s="0" t="inlineStr">
         <is>
           <t>Bank of England</t>
         </is>
       </c>
-      <c r="B1491" t="inlineStr">
+      <c r="B1491" s="0" t="inlineStr">
         <is>
           <t>Bank of England sets out approach to tokenised collateral in central clearing</t>
         </is>
       </c>
-      <c r="C1491" t="inlineStr">
+      <c r="C1491" s="0" t="inlineStr">
         <is>
           <t>https://www.bankofengland.co.uk/news/2026/october/bank-of-england-sets-out-approach-to-tokenised-collateral-in-central-clearing</t>
         </is>
       </c>
-      <c r="D1491" t="inlineStr">
+      <c r="D1491" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1491" t="inlineStr">
+      <c r="E1491" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1492">
-      <c r="A1492" t="inlineStr">
+      <c r="A1492" s="0" t="inlineStr">
         <is>
           <t>Bank of England publish</t>
         </is>
       </c>
-      <c r="B1492" t="inlineStr">
+      <c r="B1492" s="0" t="inlineStr">
         <is>
           <t>Bank of England Weekly Report 28 October 2026</t>
         </is>
       </c>
-      <c r="C1492" t="inlineStr">
+      <c r="C1492" s="0" t="inlineStr">
         <is>
           <t>https://www.bankofengland.co.uk/weekly-report/2026/28-october-2026</t>
         </is>
       </c>
-      <c r="D1492" t="inlineStr">
+      <c r="D1492" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1492" t="inlineStr">
+      <c r="E1492" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1493">
-      <c r="A1493" t="inlineStr">
+      <c r="A1493" s="0" t="inlineStr">
         <is>
           <t>Bank of England publish</t>
         </is>
       </c>
-      <c r="B1493" t="inlineStr">
+      <c r="B1493" s="0" t="inlineStr">
         <is>
           <t>Consultation on supervisory expectations for central counterparties seeking to accept tokenised collateral</t>
         </is>
       </c>
-      <c r="C1493" t="inlineStr">
+      <c r="C1493" s="0" t="inlineStr">
         <is>
           <t>https://www.bankofengland.co.uk/paper/2026/cp/supervisory-expectations-for-ccps-seeking-to-accept-tokenised-collateral</t>
         </is>
       </c>
-      <c r="D1493" t="inlineStr">
+      <c r="D1493" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1493" t="inlineStr">
+      <c r="E1493" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1494">
-      <c r="A1494" t="inlineStr">
+      <c r="A1494" s="0" t="inlineStr">
         <is>
           <t>ESMA</t>
         </is>
       </c>
-      <c r="B1494" t="inlineStr">
+      <c r="B1494" s="0" t="inlineStr">
         <is>
           <t>ESMA publishes latest edition of its newsletter</t>
         </is>
       </c>
-      <c r="C1494" t="inlineStr">
+      <c r="C1494" s="0" t="inlineStr">
         <is>
           <t>https://www.esma.europa.eu/press-news/esma-news/esma-publishes-latest-edition-its-newsletter-45</t>
         </is>
       </c>
-      <c r="D1494" t="inlineStr">
+      <c r="D1494" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1494" t="inlineStr">
+      <c r="E1494" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1495">
-      <c r="A1495" t="inlineStr">
+      <c r="A1495" s="0" t="inlineStr">
         <is>
           <t>ESMA</t>
         </is>
       </c>
-      <c r="B1495" t="inlineStr">
+      <c r="B1495" s="0" t="inlineStr">
         <is>
           <t>ESMA proposes simpler EU Taxonomy reporting</t>
         </is>
       </c>
-      <c r="C1495" t="inlineStr">
+      <c r="C1495" s="0" t="inlineStr">
         <is>
           <t>https://www.esma.europa.eu/press-news/esma-news/esma-proposes-simpler-eu-taxonomy-reporting</t>
         </is>
       </c>
-      <c r="D1495" t="inlineStr">
+      <c r="D1495" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1495" t="inlineStr">
+      <c r="E1495" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1496">
-      <c r="A1496" t="inlineStr">
+      <c r="A1496" s="0" t="inlineStr">
         <is>
           <t>ISDA</t>
         </is>
       </c>
-      <c r="B1496" t="inlineStr">
+      <c r="B1496" s="0" t="inlineStr">
         <is>
           <t>Moving Regulatory Reporting up a Gear with AI</t>
         </is>
       </c>
-      <c r="C1496" t="inlineStr">
+      <c r="C1496" s="0" t="inlineStr">
         <is>
           <t>https://www.isda.org/2026/10/29/moving-regulatory-reporting-up-a-gear-with-ai/</t>
         </is>
       </c>
-      <c r="D1496" t="inlineStr">
+      <c r="D1496" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1496" t="inlineStr">
+      <c r="E1496" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1497">
-      <c r="A1497" t="inlineStr">
+      <c r="A1497" s="0" t="inlineStr">
         <is>
           <t>BIS</t>
         </is>
       </c>
-      <c r="B1497" t="inlineStr">
+      <c r="B1497" s="0" t="inlineStr">
         <is>
           <t>CPMI publishes analysis on how central banks support payment system safety and efficiency and trust in money in the rapidly changing payments ecosystem</t>
         </is>
       </c>
-      <c r="C1497" t="inlineStr">
+      <c r="C1497" s="0" t="inlineStr">
         <is>
           <t>https://www.bis.org/media-releases/20261029-cpmi-publishes-analysis-how-central-banks-support-payment-system-safety-and-efficiency-and</t>
         </is>
       </c>
-      <c r="D1497" t="inlineStr">
+      <c r="D1497" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1497" t="inlineStr">
+      <c r="E1497" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1498">
-      <c r="A1498" t="inlineStr">
+      <c r="A1498" s="0" t="inlineStr">
         <is>
           <t>The Trade News</t>
         </is>
       </c>
-      <c r="B1498" t="inlineStr">
+      <c r="B1498" s="0" t="inlineStr">
         <is>
           <t>DTCC tokenisation service goes live as it ‘establishes the foundation for responsible institutional adoption at scale’</t>
         </is>
       </c>
-      <c r="C1498" t="inlineStr">
+      <c r="C1498" s="0" t="inlineStr">
         <is>
           <t>https://www.thetradenews.com/dtcc-tokenisation-service-goes-live-as-it-seeks-to-establish-the-foundation-for-responsible-institutional-adoption-at-scale/</t>
         </is>
       </c>
-      <c r="D1498" t="inlineStr">
+      <c r="D1498" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1498" t="inlineStr">
+      <c r="E1498" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1499">
-      <c r="A1499" t="inlineStr">
+      <c r="A1499" s="0" t="inlineStr">
         <is>
           <t>The Trade News</t>
         </is>
       </c>
-      <c r="B1499" t="inlineStr">
+      <c r="B1499" s="0" t="inlineStr">
         <is>
           <t>Ripple and Robinhood partner to enhance institutional access to digital assets and treasury operations</t>
         </is>
       </c>
-      <c r="C1499" t="inlineStr">
+      <c r="C1499" s="0" t="inlineStr">
         <is>
           <t>https://www.thetradenews.com/ripple-and-robinhood-partner-to-enhance-institutional-access-to-digital-assets-and-treasury-operations/</t>
         </is>
       </c>
-      <c r="D1499" t="inlineStr">
+      <c r="D1499" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E1499" t="inlineStr">
+      <c r="E1499" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1500">
-      <c r="A1500" t="inlineStr">
+      <c r="A1500" s="0" t="inlineStr">
         <is>
           <t>The Trade News</t>
         </is>
       </c>
-      <c r="B1500" t="inlineStr">
+      <c r="B1500" s="0" t="inlineStr">
         <is>
           <t>SGX and Philippine Stock Exchange join forces to boost Asian capital market ties</t>
         </is>
       </c>
-      <c r="C1500" t="inlineStr">
+      <c r="C1500" s="0" t="inlineStr">
         <is>
           <t>https://www.thetradenews.com/sgx-and-philippine-stock-exchange-join-forces-to-boost-asian-capital-market-ties/</t>
         </is>
       </c>
-      <c r="D1500" t="inlineStr">
+      <c r="D1500" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1500" t="inlineStr">
+      <c r="E1500" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1501">
-      <c r="A1501" t="inlineStr">
+      <c r="A1501" s="0" t="inlineStr">
         <is>
           <t>The Trade News</t>
         </is>
       </c>
-      <c r="B1501" t="inlineStr">
+      <c r="B1501" s="0" t="inlineStr">
         <is>
           <t>‘Big Bang’ at 40: Are capital markets on the cusp of another revolution?</t>
         </is>
       </c>
-      <c r="C1501" t="inlineStr">
+      <c r="C1501" s="0" t="inlineStr">
         <is>
           <t>https://www.thetradenews.com/big-bang-at-40-are-capital-markets-on-the-cusp-of-another-revolution/</t>
         </is>
       </c>
-      <c r="D1501" t="inlineStr">
+      <c r="D1501" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="E1501" t="inlineStr">
+      <c r="E1501" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1502">
-      <c r="A1502" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1502" t="inlineStr">
+      <c r="A1502" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1502" s="0" t="inlineStr">
         <is>
           <t>ICE Invests in TradeXYZ to Build Regulated Perpetual Market</t>
         </is>
       </c>
-      <c r="C1502" t="inlineStr">
+      <c r="C1502" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/ice-invests-in-tradexyz-to-build-regulated-perpetual-market/</t>
         </is>
       </c>
-      <c r="D1502" t="inlineStr">
+      <c r="D1502" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1502" t="inlineStr">
+      <c r="E1502" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1503">
-      <c r="A1503" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1503" t="inlineStr">
+      <c r="A1503" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1503" s="0" t="inlineStr">
         <is>
           <t>State Street Advances Daily NAV for Private Markets</t>
         </is>
       </c>
-      <c r="C1503" t="inlineStr">
+      <c r="C1503" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/state-street-advances-daily-nav-for-private-markets/</t>
         </is>
       </c>
-      <c r="D1503" t="inlineStr">
+      <c r="D1503" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1503" t="inlineStr">
+      <c r="E1503" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1504">
-      <c r="A1504" t="inlineStr">
-        <is>
-          <t>Markets Media</t>
-        </is>
-      </c>
-      <c r="B1504" t="inlineStr">
+      <c r="A1504" s="0" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1504" s="0" t="inlineStr">
         <is>
           <t>Chainlink, S&amp;P Bring Vault Assessments Onchain</t>
         </is>
       </c>
-      <c r="C1504" t="inlineStr">
+      <c r="C1504" s="0" t="inlineStr">
         <is>
           <t>https://www.marketsmedia.com/chainlink-sp-global-ratings-bring-vault-assessments-onchain/</t>
         </is>
       </c>
-      <c r="D1504" t="inlineStr">
+      <c r="D1504" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1504" t="inlineStr">
+      <c r="E1504" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1505">
-      <c r="A1505" t="inlineStr">
+      <c r="A1505" s="0" t="inlineStr">
         <is>
           <t>Risk.net</t>
         </is>
       </c>
-      <c r="B1505" t="inlineStr">
+      <c r="B1505" s="0" t="inlineStr">
         <is>
           <t>Non-bank dealers urge rethink on FICC default fund reshuffle</t>
         </is>
       </c>
-      <c r="C1505" t="inlineStr">
+      <c r="C1505" s="0" t="inlineStr">
         <is>
           <t>https://www.risk.net/risk-management/7964301/non-bank-dealers-urge-rethink-on-ficc-default-fund-reshuffle</t>
         </is>
       </c>
-      <c r="D1505" t="inlineStr">
+      <c r="D1505" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1505" t="inlineStr">
+      <c r="E1505" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1506">
-      <c r="A1506" t="inlineStr">
+      <c r="A1506" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1506" t="inlineStr">
+      <c r="B1506" s="0" t="inlineStr">
         <is>
           <t>Japan’s Progmat aims to tokenize bilateral JGB repo in Canton sandbox</t>
         </is>
       </c>
-      <c r="C1506" t="inlineStr">
+      <c r="C1506" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/japans-progmat-aims-to-tokenize-bilateral-jgb-repo-in-canton-sandbox/</t>
         </is>
       </c>
-      <c r="D1506" t="inlineStr">
+      <c r="D1506" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1506" t="inlineStr">
+      <c r="E1506" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1507">
-      <c r="A1507" t="inlineStr">
+      <c r="A1507" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1507" t="inlineStr">
+      <c r="B1507" s="0" t="inlineStr">
         <is>
           <t>UK DMO introduces standing repo facility and £250mn collateral pool</t>
         </is>
       </c>
-      <c r="C1507" t="inlineStr">
+      <c r="C1507" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/uk-dmo-introduces-standing-repo-facility-and-250mn-collateral-pool/</t>
         </is>
       </c>
-      <c r="D1507" t="inlineStr">
+      <c r="D1507" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1507" t="inlineStr">
+      <c r="E1507" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1508">
-      <c r="A1508" t="inlineStr">
+      <c r="A1508" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1508" t="inlineStr">
+      <c r="B1508" s="0" t="inlineStr">
         <is>
           <t>Ascend and M1X Global transact first repo using USDM1 collateral</t>
         </is>
       </c>
-      <c r="C1508" t="inlineStr">
+      <c r="C1508" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/ascend-and-m1x-global-transact-first-repo-using-usdm1-collateral/</t>
         </is>
       </c>
-      <c r="D1508" t="inlineStr">
+      <c r="D1508" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1508" t="inlineStr">
+      <c r="E1508" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1509">
-      <c r="A1509" t="inlineStr">
+      <c r="A1509" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1509" t="inlineStr">
+      <c r="B1509" s="0" t="inlineStr">
         <is>
           <t>The Investor: Vietnam margin lending hits record highs</t>
         </is>
       </c>
-      <c r="C1509" t="inlineStr">
+      <c r="C1509" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/the-investor-vietnam-margin-lending-hits-record-highs/</t>
         </is>
       </c>
-      <c r="D1509" t="inlineStr">
+      <c r="D1509" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1509" t="inlineStr">
+      <c r="E1509" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1510">
-      <c r="A1510" t="inlineStr">
+      <c r="A1510" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1510" t="inlineStr">
+      <c r="B1510" s="0" t="inlineStr">
         <is>
           <t>BoE mulls how to supervise tokenized collateral for CCPs</t>
         </is>
       </c>
-      <c r="C1510" t="inlineStr">
+      <c r="C1510" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/boe-mulls-how-to-supervise-tokenized-collateral-for-ccps/</t>
         </is>
       </c>
-      <c r="D1510" t="inlineStr">
+      <c r="D1510" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1510" t="inlineStr">
+      <c r="E1510" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1511">
-      <c r="A1511" t="inlineStr">
+      <c r="A1511" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1511" t="inlineStr">
+      <c r="B1511" s="0" t="inlineStr">
         <is>
           <t>ISDA analyzes tokenized collateral under IFRS and US GAAP for SFTs</t>
         </is>
       </c>
-      <c r="C1511" t="inlineStr">
+      <c r="C1511" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/isda-analyzes-tokenized-collateral-under-ifrs-and-us-gaap-for-sfts/</t>
         </is>
       </c>
-      <c r="D1511" t="inlineStr">
+      <c r="D1511" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1511" t="inlineStr">
+      <c r="E1511" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1512">
-      <c r="A1512" t="inlineStr">
+      <c r="A1512" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1512" t="inlineStr">
+      <c r="B1512" s="0" t="inlineStr">
         <is>
           <t>Tradeweb money markets ADV up 6% y/y at $1.1tn in Q3 2026</t>
         </is>
       </c>
-      <c r="C1512" t="inlineStr">
+      <c r="C1512" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/tradeweb-money-markets-adv-up-6-y-y-at-1-1tn-in-q3-2026/</t>
         </is>
       </c>
-      <c r="D1512" t="inlineStr">
+      <c r="D1512" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1512" t="inlineStr">
+      <c r="E1512" s="0" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="1513">
-      <c r="A1513" t="inlineStr">
+      <c r="A1513" s="0" t="inlineStr">
         <is>
           <t>Finadium</t>
         </is>
       </c>
-      <c r="B1513" t="inlineStr">
+      <c r="B1513" s="0" t="inlineStr">
         <is>
           <t>ISDA to deploy four more AI agents for regulatory reporting</t>
         </is>
       </c>
-      <c r="C1513" t="inlineStr">
+      <c r="C1513" s="0" t="inlineStr">
         <is>
           <t>https://finadium.com/isda-to-deploy-four-more-ai-agents-for-regulatory-reporting/</t>
         </is>
       </c>
-      <c r="D1513" t="inlineStr">
+      <c r="D1513" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="E1513" t="inlineStr">
+      <c r="E1513" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>Bank of England publish</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Agents' summary of business conditions - October 2026</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>https://www.bankofengland.co.uk/agents-summary/2026/october-2026</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>ISDA</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>ISDA Publishes ISDA SIMM® Methodology, Version 2.9+2606</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>https://www.isda.org/2026/10/30/isda-publishes-isda-simm-methodology-version-2-92606/</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>The Trade News</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Quod Financial launches AI workflow tool for trading desks</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>https://www.thetradenews.com/quod-financial-launches-ai-workflow-tool-for-trading-desks/</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Cboe Has “First Mover Advantage’ in KPI Contracts</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/cboe-has-first-mover-advantage-in-kpi-contracts/</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Bank of England Consults on Tokenised Collateral</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/bank-of-england-consults-on-tokenised-collateral/</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>MIAX Reports Net Revenue Increase of 20%</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/miax-report-net-revenue-increase-of-20/</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>Markets Media</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Tradeweb Average Daily Volume Increases 22.4%</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>https://www.marketsmedia.com/tradeweb-average-daily-volume-increases-22-4-year-over-year/</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>Finadium</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>US SEC issues UST repo clearing exemptive relief</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>https://finadium.com/us-sec-issues-ust-repo-clearing-exemptive-relief/</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
         <is>
           <t>No</t>
         </is>
